--- a/quote_automation/assets/weight_based_quote_template.xlsx
+++ b/quote_automation/assets/weight_based_quote_template.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="174" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="175" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -146,6 +146,11 @@
       <color rgb="FFFF0000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <charset val="128"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -838,7 +843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -1365,6 +1370,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2587,6 +2598,15 @@
       <c r="Q8" s="75" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
+      <c r="C9" s="189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（税込10%）：￥</t>
+        </is>
+      </c>
+      <c r="D9" s="190">
+        <f>ROUND(D8*1.1,0)</f>
+        <v/>
+      </c>
       <c r="O9" s="70" t="n"/>
       <c r="Q9" s="70" t="n"/>
     </row>
